--- a/exports/SOLARINDS_full_report.xlsx
+++ b/exports/SOLARINDS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.29</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44572.55208333334</v>
+        <v>44573.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2275</v>
+        <v>2209.45</v>
       </c>
       <c r="I2" t="n">
         <v>2246.53</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.06</v>
+        <v>-4.89</v>
       </c>
       <c r="L2" t="n">
-        <v>2.23</v>
+        <v>6.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34</v>
+        <v>1.98</v>
       </c>
       <c r="N2" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
         <v>-0.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>5.98</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44585.55208333334</v>
+        <v>44586.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2326</v>
+        <v>2361.65</v>
       </c>
       <c r="I3" t="n">
         <v>2341.6707273</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.28</v>
+        <v>-6.89</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9</v>
+        <v>7.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.36</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>7.95</v>
       </c>
       <c r="O3" t="n">
         <v>-2.42</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.38541666666</v>
+        <v>44603.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>2268.05</v>
+        <v>2248.7</v>
       </c>
       <c r="I4" t="n">
         <v>2250.974472786781</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.96</v>
+        <v>-4.78</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.92</v>
       </c>
       <c r="M4" t="n">
         <v>0.61</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.55208333334</v>
+        <v>44629.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2315</v>
+        <v>2394.9</v>
       </c>
       <c r="I5" t="n">
         <v>2390.8399591313</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.95</v>
+        <v>-6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>4.86</v>
+        <v>7.08</v>
       </c>
       <c r="M5" t="n">
         <v>1.24</v>
       </c>
       <c r="N5" t="n">
-        <v>3.71</v>
+        <v>4.97</v>
       </c>
       <c r="O5" t="n">
         <v>-1.9</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44676.38541666666</v>
+        <v>44676.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>2896.85</v>
+        <v>2847</v>
       </c>
       <c r="I6" t="n">
         <v>2859.288310072257</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>20.96</v>
+        <v>18.88</v>
       </c>
       <c r="L6" t="n">
         <v>4.27</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>6.38</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2927.4</v>
+        <v>2994</v>
       </c>
       <c r="I7" t="n">
         <v>2937.34174289176</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.82</v>
+        <v>-5.16</v>
       </c>
       <c r="L7" t="n">
-        <v>3.61</v>
+        <v>10.54</v>
       </c>
       <c r="M7" t="n">
-        <v>1.78</v>
+        <v>4.87</v>
       </c>
       <c r="N7" t="n">
         <v>6.45</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.89</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44693.38541666666</v>
+        <v>44693.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2790</v>
+        <v>2780</v>
       </c>
       <c r="I8" t="n">
         <v>2787.624900021775</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.81</v>
+        <v>-7.15</v>
       </c>
       <c r="L8" t="n">
-        <v>7.96</v>
+        <v>8.07</v>
       </c>
       <c r="M8" t="n">
         <v>0.67</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44719.55208333334</v>
+        <v>44720.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2780</v>
+        <v>2825.1</v>
       </c>
       <c r="I9" t="n">
         <v>2818.43569024268</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="L9" t="n">
         <v>7.01</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2750</v>
+        <v>2699.95</v>
       </c>
       <c r="I10" t="n">
         <v>2701.539385199957</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.66</v>
+        <v>-4.43</v>
       </c>
       <c r="L10" t="n">
         <v>7.25</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2800</v>
+        <v>2950</v>
       </c>
       <c r="I11" t="n">
         <v>2859.203288292736</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.71</v>
+        <v>-9.26</v>
       </c>
       <c r="L11" t="n">
-        <v>3.71</v>
+        <v>10.14</v>
       </c>
       <c r="M11" t="n">
         <v>1.64</v>
       </c>
       <c r="N11" t="n">
-        <v>3.33</v>
+        <v>6.79</v>
       </c>
       <c r="O11" t="n">
         <v>-1.74</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.76</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3723.45</v>
+        <v>3545.8</v>
       </c>
       <c r="I12" t="n">
         <v>3603.324758787838</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K12" t="n">
-        <v>26.22</v>
+        <v>20.2</v>
       </c>
       <c r="L12" t="n">
         <v>4.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0.77</v>
+        <v>1.62</v>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>7.98</v>
       </c>
       <c r="O12" t="n">
         <v>6.79</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44833.55208333334</v>
+        <v>44834.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3750.1</v>
+        <v>3857</v>
       </c>
       <c r="I13" t="n">
         <v>3793.938576272926</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.76</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.46</v>
+        <v>11.91</v>
       </c>
       <c r="M13" t="n">
         <v>1.41</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>4.59</v>
       </c>
       <c r="O13" t="n">
         <v>-7.98</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44847.38541666666</v>
+        <v>44847.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>3854.9</v>
+        <v>3826.3</v>
       </c>
       <c r="I14" t="n">
         <v>3833.466598195078</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.05</v>
+        <v>-0.8</v>
       </c>
       <c r="L14" t="n">
         <v>3.4</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.18</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>4018</v>
+        <v>4099.9</v>
       </c>
       <c r="I15" t="n">
         <v>4090.190681743999</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.01</v>
+        <v>-7.15</v>
       </c>
       <c r="L15" t="n">
-        <v>7.12</v>
+        <v>9.77</v>
       </c>
       <c r="M15" t="n">
         <v>2.35</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.83</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3950</v>
+        <v>3947</v>
       </c>
       <c r="I16" t="n">
         <v>3947.706215694921</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.66</v>
+        <v>-3.73</v>
       </c>
       <c r="L16" t="n">
-        <v>4.39</v>
+        <v>4.51</v>
       </c>
       <c r="M16" t="n">
         <v>0.37</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.62</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3889.8</v>
+        <v>4035.8</v>
       </c>
       <c r="I17" t="n">
         <v>3926.052363723009</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>1.45</v>
+        <v>-2.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.91</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="N17" t="n">
-        <v>4.56</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>-0.15</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.58</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>4030.25</v>
+        <v>4006.3</v>
       </c>
       <c r="I18" t="n">
         <v>4014.669504394289</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.14</v>
+        <v>-0.73</v>
       </c>
       <c r="L18" t="n">
         <v>3.66</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>4166</v>
+        <v>4355.65</v>
       </c>
       <c r="I19" t="n">
         <v>4250.717522107077</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.99</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>4.78</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>0.93</v>
       </c>
       <c r="N19" t="n">
-        <v>0.92</v>
+        <v>5.38</v>
       </c>
       <c r="O19" t="n">
         <v>0.89</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44943.55208333334</v>
+        <v>44944.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>4282</v>
+        <v>4237.85</v>
       </c>
       <c r="I20" t="n">
         <v>4258.845493251247</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.69</v>
+        <v>-2.7</v>
       </c>
       <c r="L20" t="n">
         <v>3.8</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.79</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3660.05</v>
+        <v>3981.85</v>
       </c>
       <c r="I21" t="n">
         <v>3837.437877778587</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>13.63</v>
+        <v>6.04</v>
       </c>
       <c r="L21" t="n">
         <v>3.39</v>
@@ -1638,7 +1889,7 @@
         <v>1.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.33</v>
+        <v>8.69</v>
       </c>
       <c r="O21" t="n">
         <v>-1.12</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.21</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3808.9</v>
+        <v>3730</v>
       </c>
       <c r="I22" t="n">
         <v>3773.259993389469</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.34</v>
+        <v>-6.32</v>
       </c>
       <c r="L22" t="n">
         <v>7.91</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.47</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45034.38541666666</v>
+        <v>45034.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>3860</v>
+        <v>3865</v>
       </c>
       <c r="I23" t="n">
         <v>3861.069200611716</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.49</v>
+        <v>-3.62</v>
       </c>
       <c r="L23" t="n">
         <v>6.7</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.54</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3835.5</v>
+        <v>3787.95</v>
       </c>
       <c r="I24" t="n">
         <v>3788.257247608429</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>65</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.76</v>
+        <v>-1.99</v>
       </c>
       <c r="L24" t="n">
         <v>5.16</v>
@@ -1809,7 +2096,7 @@
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
         <v>0.13</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45126.38541666666</v>
+        <v>45126.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3701.9</v>
+        <v>3703</v>
       </c>
       <c r="I25" t="n">
         <v>3702.798269805957</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="L25" t="n">
         <v>1.64</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.13</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45175.55208333334</v>
+        <v>45176.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4602.2</v>
+        <v>4543.85</v>
       </c>
       <c r="I26" t="n">
         <v>4598.667024938434</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>24.28</v>
+        <v>22.71</v>
       </c>
       <c r="L26" t="n">
         <v>0.63</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.41</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>4700</v>
+        <v>4844.95</v>
       </c>
       <c r="I27" t="n">
         <v>4806.697833683062</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.44</v>
+        <v>-6.63</v>
       </c>
       <c r="L27" t="n">
-        <v>4.68</v>
+        <v>7.29</v>
       </c>
       <c r="M27" t="n">
         <v>1.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="O27" t="n">
         <v>-1.24</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.37</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>5170</v>
+        <v>5073.4</v>
       </c>
       <c r="I28" t="n">
         <v>5112.418792790546</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K28" t="n">
-        <v>6.71</v>
+        <v>4.72</v>
       </c>
       <c r="L28" t="n">
         <v>2.99</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.51</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>5325</v>
+        <v>5340</v>
       </c>
       <c r="I29" t="n">
         <v>5335.629377025492</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.96</v>
+        <v>-5.25</v>
       </c>
       <c r="L29" t="n">
         <v>6.1</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.84</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>6960</v>
+        <v>6740</v>
       </c>
       <c r="I30" t="n">
         <v>6773.744201498424</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>30.34</v>
+        <v>26.22</v>
       </c>
       <c r="L30" t="n">
         <v>0.97</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45268.55208333334</v>
+        <v>45271.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>6299</v>
+        <v>6520</v>
       </c>
       <c r="I31" t="n">
         <v>6461.392288795576</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>6.54</v>
+        <v>3.26</v>
       </c>
       <c r="L31" t="n">
         <v>4.54</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.9</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>6979.55</v>
+        <v>6752.35</v>
       </c>
       <c r="I32" t="n">
         <v>6866.023000793171</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K32" t="n">
-        <v>7.05</v>
+        <v>3.56</v>
       </c>
       <c r="L32" t="n">
         <v>5.67</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.35</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45328.38541666666</v>
+        <v>45328.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>6711.9</v>
+        <v>6770</v>
       </c>
       <c r="I33" t="n">
         <v>6735.41997635665</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6</v>
+        <v>-0.26</v>
       </c>
       <c r="L33" t="n">
         <v>4.41</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>7761</v>
+        <v>7058.9</v>
       </c>
       <c r="I34" t="n">
         <v>7104.384028314455</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>14.64</v>
+        <v>4.27</v>
       </c>
       <c r="L34" t="n">
         <v>3.23</v>
@@ -2379,7 +2786,7 @@
         <v>0.39</v>
       </c>
       <c r="N34" t="n">
-        <v>3.71</v>
+        <v>7.23</v>
       </c>
       <c r="O34" t="n">
         <v>2.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45365.38541666666</v>
+        <v>45365.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>7831.05</v>
+        <v>8352</v>
       </c>
       <c r="I35" t="n">
         <v>7883.561437065291</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.94</v>
+        <v>-18.32</v>
       </c>
       <c r="L35" t="n">
-        <v>14.55</v>
+        <v>18.57</v>
       </c>
       <c r="M35" t="n">
         <v>0.98</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>16.06</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>8595</v>
+        <v>8302.75</v>
       </c>
       <c r="I36" t="n">
         <v>8584.955105412246</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>2.91</v>
+        <v>-0.59</v>
       </c>
       <c r="L36" t="n">
         <v>6.45</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>8352</v>
+        <v>8968.15</v>
       </c>
       <c r="I37" t="n">
         <v>8880.281278546616</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.59</v>
+        <v>-8.01</v>
       </c>
       <c r="L37" t="n">
-        <v>4.01</v>
+        <v>9.59</v>
       </c>
       <c r="M37" t="n">
         <v>1.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0.02</v>
+        <v>6.56</v>
       </c>
       <c r="O37" t="n">
         <v>-2.85</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>9362</v>
+        <v>9284.5</v>
       </c>
       <c r="I38" t="n">
         <v>9337.724038672664</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>4.39</v>
+        <v>3.53</v>
       </c>
       <c r="L38" t="n">
         <v>6.76</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.09</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>9745.25</v>
+        <v>10085.9</v>
       </c>
       <c r="I39" t="n">
         <v>10035.40329878238</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.96</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>5.55</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>2.86</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.49</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45447.38541666666</v>
+        <v>45447.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>9089.75</v>
+        <v>8695</v>
       </c>
       <c r="I40" t="n">
         <v>8929.265781491791</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-9.880000000000001</v>
+        <v>-13.79</v>
       </c>
       <c r="L40" t="n">
         <v>21.79</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>21.28</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>10130</v>
+        <v>10873.85</v>
       </c>
       <c r="I41" t="n">
         <v>10289.0057230331</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-16.5</v>
+        <v>-25.06</v>
       </c>
       <c r="L41" t="n">
-        <v>17.6</v>
+        <v>28.69</v>
       </c>
       <c r="M41" t="n">
         <v>3.54</v>
       </c>
       <c r="N41" t="n">
-        <v>4.03</v>
+        <v>7.9</v>
       </c>
       <c r="O41" t="n">
         <v>-12.49</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.77</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>11451</v>
+        <v>10770.05</v>
       </c>
       <c r="I42" t="n">
         <v>11159.75370861457</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>5.31</v>
+        <v>-0.95</v>
       </c>
       <c r="L42" t="n">
         <v>6.19</v>
       </c>
       <c r="M42" t="n">
-        <v>-0</v>
+        <v>1.27</v>
       </c>
       <c r="N42" t="n">
-        <v>3.06</v>
+        <v>4.38</v>
       </c>
       <c r="O42" t="n">
         <v>7.9</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45533.55208333334</v>
+        <v>45534.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>10430</v>
+        <v>10856.3</v>
       </c>
       <c r="I43" t="n">
         <v>10814.92748987622</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K43" t="n">
-        <v>3.16</v>
+        <v>-0.8</v>
       </c>
       <c r="L43" t="n">
         <v>6.3</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>10988.2</v>
+        <v>10905</v>
       </c>
       <c r="I44" t="n">
         <v>10926.82189999478</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>1.21</v>
+        <v>0.45</v>
       </c>
       <c r="L44" t="n">
         <v>4.13</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.83</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45623.55208333334</v>
+        <v>45624.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>10305</v>
+        <v>10727</v>
       </c>
       <c r="I45" t="n">
         <v>10448.9831589683</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>5.5</v>
+        <v>1.63</v>
       </c>
       <c r="L45" t="n">
         <v>6.6</v>
@@ -3006,7 +3545,7 @@
         <v>2.11</v>
       </c>
       <c r="N45" t="n">
-        <v>5.71</v>
+        <v>5.77</v>
       </c>
       <c r="O45" t="n">
         <v>-3.49</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>10270</v>
+        <v>10082.95</v>
       </c>
       <c r="I46" t="n">
         <v>10179.13697187264</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.26</v>
+        <v>-6</v>
       </c>
       <c r="L46" t="n">
         <v>6.27</v>
@@ -3063,7 +3614,7 @@
         <v>1.66</v>
       </c>
       <c r="N46" t="n">
-        <v>2.25</v>
+        <v>4.67</v>
       </c>
       <c r="O46" t="n">
         <v>5.77</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>6.96</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>9539</v>
+        <v>9714.1</v>
       </c>
       <c r="I47" t="n">
         <v>9633.151387165248</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>5.39</v>
+        <v>3.66</v>
       </c>
       <c r="L47" t="n">
         <v>3.64</v>
       </c>
       <c r="M47" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="N47" t="n">
         <v>4.55</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.97</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>9564.75</v>
+        <v>9139</v>
       </c>
       <c r="I48" t="n">
         <v>9177.442603097494</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.54</v>
+        <v>-5.92</v>
       </c>
       <c r="L48" t="n">
-        <v>2.14</v>
+        <v>6.53</v>
       </c>
       <c r="M48" t="n">
         <v>-0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="O48" t="n">
         <v>0.64</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>9.9</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>9588.950000000001</v>
+        <v>10109.95</v>
       </c>
       <c r="I49" t="n">
         <v>9934.462145607735</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.92</v>
+        <v>-10.62</v>
       </c>
       <c r="L49" t="n">
-        <v>5.7</v>
+        <v>12.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0.41</v>
+        <v>4.32</v>
       </c>
       <c r="N49" t="n">
-        <v>3.55</v>
+        <v>5.35</v>
       </c>
       <c r="O49" t="n">
         <v>-2.56</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45693.55208333334</v>
+        <v>45694.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>9710</v>
+        <v>9235.450000000001</v>
       </c>
       <c r="I50" t="n">
         <v>9442.346266061553</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.96</v>
+        <v>-8.65</v>
       </c>
       <c r="L50" t="n">
-        <v>6.5</v>
+        <v>10.73</v>
       </c>
       <c r="M50" t="n">
         <v>0.43</v>
       </c>
       <c r="N50" t="n">
-        <v>5.27</v>
+        <v>6.18</v>
       </c>
       <c r="O50" t="n">
         <v>5.35</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>14.29</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>9054.25</v>
+        <v>9255</v>
       </c>
       <c r="I51" t="n">
         <v>9088.982507109105</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>1.96</v>
+        <v>-0.21</v>
       </c>
       <c r="L51" t="n">
         <v>7.15</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.21</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>11000</v>
+        <v>10664.75</v>
       </c>
       <c r="I52" t="n">
         <v>10684.15715119733</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K52" t="n">
-        <v>18.85</v>
+        <v>15.23</v>
       </c>
       <c r="L52" t="n">
         <v>2.18</v>
       </c>
       <c r="M52" t="n">
-        <v>0.53</v>
+        <v>6.52</v>
       </c>
       <c r="N52" t="n">
         <v>2.44</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>10915.45</v>
+        <v>11378.5</v>
       </c>
       <c r="I53" t="n">
         <v>11169.12971177714</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.35</v>
+        <v>-6.69</v>
       </c>
       <c r="L53" t="n">
-        <v>3.13</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>0.74</v>
+        <v>1.61</v>
       </c>
       <c r="N53" t="n">
-        <v>1.48</v>
+        <v>3.59</v>
       </c>
       <c r="O53" t="n">
         <v>-1.82</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.51</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45845.38541666666</v>
+        <v>45845.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>16776</v>
+        <v>16720</v>
       </c>
       <c r="I54" t="n">
         <v>16769.77023374279</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>87</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>47.44</v>
+        <v>46.94</v>
       </c>
       <c r="L54" t="n">
         <v>2.53</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.86</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45873.55208333334</v>
+        <v>45874.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>14430</v>
+        <v>14577</v>
       </c>
       <c r="I55" t="n">
         <v>14570.90068899849</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>13.7</v>
+        <v>12.82</v>
       </c>
       <c r="L55" t="n">
         <v>0.82</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>14641</v>
+        <v>14213</v>
       </c>
       <c r="I56" t="n">
         <v>14235.05661543795</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>0.44</v>
+        <v>-2.5</v>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="M56" t="n">
         <v>0.48</v>
       </c>
       <c r="N56" t="n">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="O56" t="n">
         <v>3.6</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.32</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45915.55208333334</v>
+        <v>45916.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>14485</v>
+        <v>14588</v>
       </c>
       <c r="I57" t="n">
         <v>14559.07901474424</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.91</v>
+        <v>-2.64</v>
       </c>
       <c r="L57" t="n">
         <v>3.21</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.53</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>14118</v>
+        <v>14003</v>
       </c>
       <c r="I58" t="n">
         <v>14096.44296927131</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.22</v>
+        <v>-4.01</v>
       </c>
       <c r="L58" t="n">
-        <v>3.83</v>
+        <v>4.03</v>
       </c>
       <c r="M58" t="n">
         <v>0.41</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>5.08</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>13845</v>
+        <v>14131</v>
       </c>
       <c r="I59" t="n">
         <v>14054.50322578845</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>1.13</v>
+        <v>-0.91</v>
       </c>
       <c r="L59" t="n">
         <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="N59" t="n">
         <v>2.71</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.52</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>13748</v>
+        <v>13640</v>
       </c>
       <c r="I60" t="n">
         <v>13678.48291031069</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.71</v>
+        <v>-3.47</v>
       </c>
       <c r="L60" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="M60" t="n">
         <v>0.7</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>4.34</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>13810</v>
+        <v>14127</v>
       </c>
       <c r="I61" t="n">
         <v>13940.92518629064</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.25</v>
+        <v>-3.57</v>
       </c>
       <c r="L61" t="n">
-        <v>3.26</v>
+        <v>4.44</v>
       </c>
       <c r="M61" t="n">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
         <v>3.21</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>6.92</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45985.55208333334</v>
+        <v>45986.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>13380</v>
+        <v>13296</v>
       </c>
       <c r="I62" t="n">
         <v>13308.91557248168</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.29</v>
+        <v>-5.88</v>
       </c>
       <c r="L62" t="n">
-        <v>5.73</v>
+        <v>5.95</v>
       </c>
       <c r="M62" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="N62" t="n">
         <v>2.7</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>5.6</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>11940</v>
+        <v>12429</v>
       </c>
       <c r="I63" t="n">
         <v>12231.425231175</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K63" t="n">
-        <v>10.2</v>
+        <v>6.52</v>
       </c>
       <c r="L63" t="n">
         <v>2.21</v>
@@ -4032,7 +4787,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>5.71</v>
       </c>
       <c r="O63" t="n">
         <v>-0.75</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>12320</v>
+        <v>11919</v>
       </c>
       <c r="I64" t="n">
         <v>11985.23706167524</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.88</v>
+        <v>-4.1</v>
       </c>
       <c r="L64" t="n">
-        <v>4.66</v>
+        <v>4.87</v>
       </c>
       <c r="M64" t="n">
         <v>0.02</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.46</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>12734</v>
+        <v>12818</v>
       </c>
       <c r="I65" t="n">
         <v>12807.65241383487</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.84</v>
+        <v>-7.54</v>
       </c>
       <c r="L65" t="n">
         <v>8.41</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.58</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>13021</v>
+        <v>12659</v>
       </c>
       <c r="I66" t="n">
         <v>12722.54585676364</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>1.58</v>
+        <v>-1.24</v>
       </c>
       <c r="L66" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="M66" t="n">
         <v>0.19</v>
       </c>
       <c r="N66" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
       </c>
       <c r="O66" t="n">
         <v>0.91</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>9.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>12832</v>
+        <v>13613</v>
       </c>
       <c r="I67" t="n">
         <v>13287.38218855718</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.37</v>
+        <v>-7.54</v>
       </c>
       <c r="L67" t="n">
-        <v>4.11</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M67" t="n">
         <v>1.13</v>
       </c>
       <c r="N67" t="n">
-        <v>3.04</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O67" t="n">
         <v>-2.72</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>9.82</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>14257</v>
+        <v>13985</v>
       </c>
       <c r="I68" t="n">
         <v>14126.46124337802</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K68" t="n">
-        <v>4.73</v>
+        <v>2.73</v>
       </c>
       <c r="L68" t="n">
         <v>9.1</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.99</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>13050</v>
+        <v>13237</v>
       </c>
       <c r="I69" t="n">
         <v>13180.92676253216</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K69" t="n">
-        <v>6.69</v>
+        <v>5.35</v>
       </c>
       <c r="L69" t="n">
         <v>3.59</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>18103</v>
+        <v>17655</v>
       </c>
       <c r="I70" t="n">
         <v>17764.33006548897</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>65</v>
+        <v>65.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>36.76</v>
+        <v>33.38</v>
       </c>
       <c r="L70" t="n">
         <v>2.15</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.15</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46191.55208333334</v>
+        <v>46192.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>17770</v>
+        <v>18148</v>
       </c>
       <c r="I71" t="n">
         <v>17943.52888765037</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.65</v>
+        <v>-2.79</v>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="M71" t="n">
         <v>1.61</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>6.94</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>18005</v>
+        <v>17344</v>
       </c>
       <c r="I72" t="n">
         <v>17535.94417529314</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.79</v>
+        <v>-4.43</v>
       </c>
       <c r="L72" t="n">
-        <v>4.82</v>
+        <v>6.17</v>
       </c>
       <c r="M72" t="n">
         <v>1.09</v>
       </c>
       <c r="N72" t="n">
-        <v>2.4</v>
+        <v>3.44</v>
       </c>
       <c r="O72" t="n">
         <v>1.63</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>18420</v>
+        <v>18838</v>
       </c>
       <c r="I73" t="n">
         <v>18638.64349328423</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.2</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>7.81</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M73" t="n">
         <v>0.47</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>6.12</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46232.55208333334</v>
+        <v>46233.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>18023</v>
+        <v>17975</v>
       </c>
       <c r="I74" t="n">
         <v>18004.49096059557</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.33</v>
+        <v>-4.58</v>
       </c>
       <c r="L74" t="n">
-        <v>4.33</v>
+        <v>5.22</v>
       </c>
       <c r="M74" t="n">
         <v>0.49</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>4.9</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46246.55208333334</v>
+        <v>46247.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>18669</v>
+        <v>19040</v>
       </c>
       <c r="I75" t="n">
         <v>18839.83618011883</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.86</v>
+        <v>-5.92</v>
       </c>
       <c r="L75" t="n">
-        <v>5.2</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M75" t="n">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="N75" t="n">
-        <v>1.72</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O75" t="n">
         <v>0.15</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>4.7</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>22350</v>
+        <v>19675</v>
       </c>
       <c r="I76" t="n">
         <v>21433.91307695794</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K76" t="n">
-        <v>17.38</v>
+        <v>3.34</v>
       </c>
       <c r="L76" t="n">
         <v>1.55</v>
@@ -4773,7 +5684,7 @@
         <v>3.08</v>
       </c>
       <c r="N76" t="n">
-        <v>1.75</v>
+        <v>13.91</v>
       </c>
       <c r="O76" t="n">
         <v>8.869999999999999</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>58</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7926,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7936,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7946,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.36</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.48</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.85</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47.44</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.3</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.98</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.33</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.79</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="25">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.55</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8086,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.63</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
